--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_RIGALLI-ALGINET.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_RIGALLI-ALGINET.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MARTIN FERNANDEZ</t>
+          <t>M. MARTINEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>106.2719</v>
+        <v>97.952</v>
       </c>
       <c r="E2" t="n">
-        <v>78.0292</v>
+        <v>57.3266</v>
       </c>
       <c r="F2" t="n">
-        <v>28.2425</v>
+        <v>40.6258</v>
       </c>
       <c r="G2" t="n">
-        <v>64.0545</v>
+        <v>54.9129</v>
       </c>
       <c r="H2" t="n">
-        <v>56.2945</v>
+        <v>17.0347</v>
       </c>
       <c r="I2" t="n">
-        <v>7.7597</v>
+        <v>37.8779</v>
       </c>
       <c r="J2" t="n">
-        <v>76.80459999999999</v>
+        <v>67.20180000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>63.3138</v>
+        <v>27.6213</v>
       </c>
       <c r="L2" t="n">
-        <v>13.4909</v>
+        <v>39.5804</v>
       </c>
       <c r="M2" t="n">
-        <v>-12.7504</v>
+        <v>-12.2887</v>
       </c>
       <c r="N2" t="n">
-        <v>-7.019600000000001</v>
+        <v>-10.5865</v>
       </c>
       <c r="O2" t="n">
-        <v>-5.731</v>
+        <v>-1.7024</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9435000000000004</v>
+        <v>18.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>-42.6462</v>
+        <v>-36.9852</v>
       </c>
       <c r="R2" t="n">
-        <v>41.7027</v>
+        <v>55.8552</v>
       </c>
       <c r="S2" t="n">
-        <v>42.2463</v>
+        <v>12.1247</v>
       </c>
       <c r="T2" t="n">
-        <v>35.0252</v>
+        <v>10.9789</v>
       </c>
       <c r="U2" t="n">
-        <v>7.2207</v>
+        <v>1.1453</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9146999999999998</v>
+        <v>12.0447</v>
       </c>
       <c r="W2" t="n">
-        <v>8.8451</v>
+        <v>16.1306</v>
       </c>
       <c r="X2" t="n">
-        <v>-7.9306</v>
+        <v>-4.085900000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. MARTINEZ HERNANDEZ</t>
+          <t>J. MARTIN FERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>86.6005</v>
+        <v>88.6207</v>
       </c>
       <c r="E3" t="n">
-        <v>50.1887</v>
+        <v>61.1212</v>
       </c>
       <c r="F3" t="n">
-        <v>36.4118</v>
+        <v>27.5003</v>
       </c>
       <c r="G3" t="n">
-        <v>54.9129</v>
+        <v>64.0545</v>
       </c>
       <c r="H3" t="n">
-        <v>17.0347</v>
+        <v>56.2945</v>
       </c>
       <c r="I3" t="n">
-        <v>37.8779</v>
+        <v>7.7597</v>
       </c>
       <c r="J3" t="n">
-        <v>67.20180000000001</v>
+        <v>76.80459999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>27.6213</v>
+        <v>63.3138</v>
       </c>
       <c r="L3" t="n">
-        <v>39.5804</v>
+        <v>13.4909</v>
       </c>
       <c r="M3" t="n">
-        <v>-12.2887</v>
+        <v>-12.7504</v>
       </c>
       <c r="N3" t="n">
-        <v>-10.5865</v>
+        <v>-7.019600000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.7024</v>
+        <v>-5.731</v>
       </c>
       <c r="P3" t="n">
-        <v>18.87</v>
+        <v>-0.9435000000000004</v>
       </c>
       <c r="Q3" t="n">
-        <v>-36.9852</v>
+        <v>-42.6462</v>
       </c>
       <c r="R3" t="n">
-        <v>55.8552</v>
+        <v>41.7027</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7732</v>
+        <v>24.5953</v>
       </c>
       <c r="T3" t="n">
-        <v>3.8414</v>
+        <v>18.1173</v>
       </c>
       <c r="U3" t="n">
-        <v>-3.0683</v>
+        <v>6.478499999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>12.0447</v>
+        <v>0.9146999999999998</v>
       </c>
       <c r="W3" t="n">
-        <v>16.1306</v>
+        <v>8.8451</v>
       </c>
       <c r="X3" t="n">
-        <v>-4.085900000000001</v>
+        <v>-7.9306</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>A. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>81.259</v>
+        <v>78.88249999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>57.8063</v>
+        <v>49.6348</v>
       </c>
       <c r="F4" t="n">
-        <v>23.4527</v>
+        <v>29.2478</v>
       </c>
       <c r="G4" t="n">
-        <v>25.821</v>
+        <v>19.0381</v>
       </c>
       <c r="H4" t="n">
-        <v>16.4359</v>
+        <v>15.818</v>
       </c>
       <c r="I4" t="n">
-        <v>9.384500000000001</v>
+        <v>3.220500000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>42.2173</v>
+        <v>35.456</v>
       </c>
       <c r="K4" t="n">
-        <v>28.3137</v>
+        <v>27.3938</v>
       </c>
       <c r="L4" t="n">
-        <v>13.9036</v>
+        <v>8.0626</v>
       </c>
       <c r="M4" t="n">
-        <v>-16.3963</v>
+        <v>-16.4177</v>
       </c>
       <c r="N4" t="n">
-        <v>-11.8778</v>
+        <v>-11.5755</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.5184</v>
+        <v>-4.842</v>
       </c>
       <c r="P4" t="n">
-        <v>13.209</v>
+        <v>16.4169</v>
       </c>
       <c r="Q4" t="n">
-        <v>-29.6259</v>
+        <v>-36.4191</v>
       </c>
       <c r="R4" t="n">
-        <v>42.8349</v>
+        <v>52.836</v>
       </c>
       <c r="S4" t="n">
-        <v>35.4343</v>
+        <v>13.4108</v>
       </c>
       <c r="T4" t="n">
-        <v>25.2935</v>
+        <v>8.225</v>
       </c>
       <c r="U4" t="n">
-        <v>10.1409</v>
+        <v>5.1859</v>
       </c>
       <c r="V4" t="n">
-        <v>6.7946</v>
+        <v>30.0166</v>
       </c>
       <c r="W4" t="n">
-        <v>19.9212</v>
+        <v>42.3726</v>
       </c>
       <c r="X4" t="n">
-        <v>-13.1265</v>
+        <v>-12.3562</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ZURBRIGGEN</t>
+          <t>R. MALLIK BOUNAD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>73.84950000000001</v>
+        <v>65.7989</v>
       </c>
       <c r="E5" t="n">
-        <v>42.0099</v>
+        <v>42.0491</v>
       </c>
       <c r="F5" t="n">
-        <v>31.8398</v>
+        <v>23.7496</v>
       </c>
       <c r="G5" t="n">
-        <v>19.0381</v>
+        <v>51.5854</v>
       </c>
       <c r="H5" t="n">
-        <v>15.818</v>
+        <v>47.5098</v>
       </c>
       <c r="I5" t="n">
-        <v>3.220500000000001</v>
+        <v>4.0761</v>
       </c>
       <c r="J5" t="n">
-        <v>35.456</v>
+        <v>63.0531</v>
       </c>
       <c r="K5" t="n">
-        <v>27.3938</v>
+        <v>55.3239</v>
       </c>
       <c r="L5" t="n">
-        <v>8.0626</v>
+        <v>7.7285</v>
       </c>
       <c r="M5" t="n">
-        <v>-16.4177</v>
+        <v>-11.4674</v>
       </c>
       <c r="N5" t="n">
-        <v>-11.5755</v>
+        <v>-7.8147</v>
       </c>
       <c r="O5" t="n">
-        <v>-4.842</v>
+        <v>-3.6528</v>
       </c>
       <c r="P5" t="n">
-        <v>16.4169</v>
+        <v>1.5096</v>
       </c>
       <c r="Q5" t="n">
-        <v>-36.4191</v>
+        <v>-43.5897</v>
       </c>
       <c r="R5" t="n">
-        <v>52.836</v>
+        <v>45.0993</v>
       </c>
       <c r="S5" t="n">
-        <v>8.3779</v>
+        <v>14.9342</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5998999999999999</v>
+        <v>9.739000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>7.7779</v>
+        <v>5.1954</v>
       </c>
       <c r="V5" t="n">
-        <v>30.0166</v>
+        <v>-2.2308</v>
       </c>
       <c r="W5" t="n">
-        <v>42.3726</v>
+        <v>12.8466</v>
       </c>
       <c r="X5" t="n">
-        <v>-12.3562</v>
+        <v>-15.0774</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. MALLIK BOUNAD</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>58.5257</v>
+        <v>63.2124</v>
       </c>
       <c r="E6" t="n">
-        <v>37.4246</v>
+        <v>44.7736</v>
       </c>
       <c r="F6" t="n">
-        <v>21.1014</v>
+        <v>18.4386</v>
       </c>
       <c r="G6" t="n">
-        <v>51.5854</v>
+        <v>25.821</v>
       </c>
       <c r="H6" t="n">
-        <v>47.5098</v>
+        <v>16.4359</v>
       </c>
       <c r="I6" t="n">
-        <v>4.0761</v>
+        <v>9.384500000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>63.0531</v>
+        <v>42.2173</v>
       </c>
       <c r="K6" t="n">
-        <v>55.3239</v>
+        <v>28.3137</v>
       </c>
       <c r="L6" t="n">
-        <v>7.7285</v>
+        <v>13.9036</v>
       </c>
       <c r="M6" t="n">
-        <v>-11.4674</v>
+        <v>-16.3963</v>
       </c>
       <c r="N6" t="n">
-        <v>-7.8147</v>
+        <v>-11.8778</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.6528</v>
+        <v>-4.5184</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5096</v>
+        <v>13.209</v>
       </c>
       <c r="Q6" t="n">
-        <v>-43.5897</v>
+        <v>-29.6259</v>
       </c>
       <c r="R6" t="n">
-        <v>45.0993</v>
+        <v>42.8349</v>
       </c>
       <c r="S6" t="n">
-        <v>7.6613</v>
+        <v>17.3876</v>
       </c>
       <c r="T6" t="n">
-        <v>5.1143</v>
+        <v>12.2607</v>
       </c>
       <c r="U6" t="n">
-        <v>2.547</v>
+        <v>5.1271</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.2308</v>
+        <v>6.7946</v>
       </c>
       <c r="W6" t="n">
-        <v>12.8466</v>
+        <v>19.9212</v>
       </c>
       <c r="X6" t="n">
-        <v>-15.0774</v>
+        <v>-13.1265</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>54.3683</v>
+        <v>45.2791</v>
       </c>
       <c r="E7" t="n">
-        <v>36.0593</v>
+        <v>28.5234</v>
       </c>
       <c r="F7" t="n">
-        <v>18.3091</v>
+        <v>16.7561</v>
       </c>
       <c r="G7" t="n">
         <v>12.3627</v>
@@ -1000,13 +1000,13 @@
         <v>40.5705</v>
       </c>
       <c r="S7" t="n">
-        <v>23.585</v>
+        <v>14.4958</v>
       </c>
       <c r="T7" t="n">
-        <v>18.3462</v>
+        <v>10.8104</v>
       </c>
       <c r="U7" t="n">
-        <v>5.2384</v>
+        <v>3.6853</v>
       </c>
       <c r="V7" t="n">
         <v>0.1169000000000002</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. PELUFO LOZANO</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>40.6665</v>
+        <v>41.1009</v>
       </c>
       <c r="E8" t="n">
-        <v>28.8529</v>
+        <v>22.0664</v>
       </c>
       <c r="F8" t="n">
-        <v>11.8135</v>
+        <v>19.0344</v>
       </c>
       <c r="G8" t="n">
-        <v>35.937</v>
+        <v>18.3559</v>
       </c>
       <c r="H8" t="n">
-        <v>36.8212</v>
+        <v>11.6913</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8840999999999996</v>
+        <v>6.6643</v>
       </c>
       <c r="J8" t="n">
-        <v>50.5621</v>
+        <v>37.157</v>
       </c>
       <c r="K8" t="n">
-        <v>44.2649</v>
+        <v>22.0776</v>
       </c>
       <c r="L8" t="n">
-        <v>6.2973</v>
+        <v>15.0796</v>
       </c>
       <c r="M8" t="n">
-        <v>-14.625</v>
+        <v>-18.8016</v>
       </c>
       <c r="N8" t="n">
-        <v>-7.4437</v>
+        <v>-10.3861</v>
       </c>
       <c r="O8" t="n">
-        <v>-7.1818</v>
+        <v>-8.4153</v>
       </c>
       <c r="P8" t="n">
-        <v>8.8689</v>
+        <v>-5.283599999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-33.7773</v>
+        <v>-45.8541</v>
       </c>
       <c r="R8" t="n">
-        <v>42.6462</v>
+        <v>40.5705</v>
       </c>
       <c r="S8" t="n">
-        <v>14.4155</v>
+        <v>7.6754</v>
       </c>
       <c r="T8" t="n">
-        <v>11.7493</v>
+        <v>5.068</v>
       </c>
       <c r="U8" t="n">
-        <v>2.6662</v>
+        <v>2.6075</v>
       </c>
       <c r="V8" t="n">
-        <v>-18.5547</v>
+        <v>20.3532</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3187000000000002</v>
+        <v>25.6954</v>
       </c>
       <c r="X8" t="n">
-        <v>-18.8735</v>
+        <v>-5.3422</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>V. PELUFO LOZANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>23.7032</v>
+        <v>40.4684</v>
       </c>
       <c r="E9" t="n">
-        <v>10.934</v>
+        <v>27.1797</v>
       </c>
       <c r="F9" t="n">
-        <v>12.769</v>
+        <v>13.2885</v>
       </c>
       <c r="G9" t="n">
-        <v>18.3559</v>
+        <v>35.937</v>
       </c>
       <c r="H9" t="n">
-        <v>11.6913</v>
+        <v>36.8212</v>
       </c>
       <c r="I9" t="n">
-        <v>6.6643</v>
+        <v>-0.8840999999999996</v>
       </c>
       <c r="J9" t="n">
-        <v>37.157</v>
+        <v>50.5621</v>
       </c>
       <c r="K9" t="n">
-        <v>22.0776</v>
+        <v>44.2649</v>
       </c>
       <c r="L9" t="n">
-        <v>15.0796</v>
+        <v>6.2973</v>
       </c>
       <c r="M9" t="n">
-        <v>-18.8016</v>
+        <v>-14.625</v>
       </c>
       <c r="N9" t="n">
-        <v>-10.3861</v>
+        <v>-7.4437</v>
       </c>
       <c r="O9" t="n">
-        <v>-8.4153</v>
+        <v>-7.1818</v>
       </c>
       <c r="P9" t="n">
-        <v>-5.283599999999999</v>
+        <v>8.8689</v>
       </c>
       <c r="Q9" t="n">
-        <v>-45.8541</v>
+        <v>-33.7773</v>
       </c>
       <c r="R9" t="n">
-        <v>40.5705</v>
+        <v>42.6462</v>
       </c>
       <c r="S9" t="n">
-        <v>-9.7225</v>
+        <v>14.217</v>
       </c>
       <c r="T9" t="n">
-        <v>-6.0648</v>
+        <v>10.0763</v>
       </c>
       <c r="U9" t="n">
-        <v>-3.658</v>
+        <v>4.1407</v>
       </c>
       <c r="V9" t="n">
-        <v>20.3532</v>
+        <v>-18.5547</v>
       </c>
       <c r="W9" t="n">
-        <v>25.6954</v>
+        <v>0.3187000000000002</v>
       </c>
       <c r="X9" t="n">
-        <v>-5.3422</v>
+        <v>-18.8735</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. DALMAU ROIG</t>
+          <t>P. SILLA TEBAR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>20.9886</v>
+        <v>29.0838</v>
       </c>
       <c r="E10" t="n">
-        <v>8.2713</v>
+        <v>14.8269</v>
       </c>
       <c r="F10" t="n">
-        <v>12.7176</v>
+        <v>14.2569</v>
       </c>
       <c r="G10" t="n">
-        <v>1.724599999999999</v>
+        <v>2.112499999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.7948</v>
+        <v>5.5479</v>
       </c>
       <c r="I10" t="n">
-        <v>4.5191</v>
+        <v>-3.435100000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>18.1419</v>
+        <v>21.5284</v>
       </c>
       <c r="K10" t="n">
-        <v>10.0146</v>
+        <v>17.4569</v>
       </c>
       <c r="L10" t="n">
-        <v>8.126999999999999</v>
+        <v>4.071300000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-16.4171</v>
+        <v>-19.4155</v>
       </c>
       <c r="N10" t="n">
-        <v>-12.8091</v>
+        <v>-11.9093</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.6079</v>
+        <v>-7.5065</v>
       </c>
       <c r="P10" t="n">
-        <v>24.7197</v>
+        <v>7.7367</v>
       </c>
       <c r="Q10" t="n">
-        <v>-20.3796</v>
+        <v>-30.5694</v>
       </c>
       <c r="R10" t="n">
-        <v>45.0993</v>
+        <v>38.3061</v>
       </c>
       <c r="S10" t="n">
-        <v>6.0946</v>
+        <v>3.9524</v>
       </c>
       <c r="T10" t="n">
-        <v>4.3588</v>
+        <v>3.738</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7356</v>
+        <v>0.2147000000000002</v>
       </c>
       <c r="V10" t="n">
-        <v>-11.55</v>
+        <v>15.2822</v>
       </c>
       <c r="W10" t="n">
-        <v>6.15</v>
+        <v>20.13</v>
       </c>
       <c r="X10" t="n">
-        <v>-17.7</v>
+        <v>-4.847800000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. SILLA TEBAR</t>
+          <t>J. DALMAU ROIG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>15.2472</v>
+        <v>27.0281</v>
       </c>
       <c r="E11" t="n">
-        <v>5.528700000000001</v>
+        <v>12.4272</v>
       </c>
       <c r="F11" t="n">
-        <v>9.7187</v>
+        <v>14.6014</v>
       </c>
       <c r="G11" t="n">
-        <v>2.112499999999999</v>
+        <v>1.724599999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>5.5479</v>
+        <v>-2.7948</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.435100000000001</v>
+        <v>4.5191</v>
       </c>
       <c r="J11" t="n">
-        <v>21.5284</v>
+        <v>18.1419</v>
       </c>
       <c r="K11" t="n">
-        <v>17.4569</v>
+        <v>10.0146</v>
       </c>
       <c r="L11" t="n">
-        <v>4.071300000000001</v>
+        <v>8.126999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-19.4155</v>
+        <v>-16.4171</v>
       </c>
       <c r="N11" t="n">
-        <v>-11.9093</v>
+        <v>-12.8091</v>
       </c>
       <c r="O11" t="n">
-        <v>-7.5065</v>
+        <v>-3.6079</v>
       </c>
       <c r="P11" t="n">
-        <v>7.7367</v>
+        <v>24.7197</v>
       </c>
       <c r="Q11" t="n">
-        <v>-30.5694</v>
+        <v>-20.3796</v>
       </c>
       <c r="R11" t="n">
-        <v>38.3061</v>
+        <v>45.0993</v>
       </c>
       <c r="S11" t="n">
-        <v>-9.8842</v>
+        <v>12.1339</v>
       </c>
       <c r="T11" t="n">
-        <v>-5.5604</v>
+        <v>8.514900000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.324</v>
+        <v>3.6191</v>
       </c>
       <c r="V11" t="n">
-        <v>15.2822</v>
+        <v>-11.55</v>
       </c>
       <c r="W11" t="n">
-        <v>20.13</v>
+        <v>6.15</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.847800000000001</v>
+        <v>-17.7</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>11.2882</v>
+        <v>12.4017</v>
       </c>
       <c r="E12" t="n">
-        <v>11.9496</v>
+        <v>12.4568</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6613000000000002</v>
+        <v>-0.0551999999999998</v>
       </c>
       <c r="G12" t="n">
         <v>10.8013</v>
@@ -1390,13 +1390,13 @@
         <v>6.415800000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.05710000000000004</v>
+        <v>1.0565</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6335</v>
+        <v>1.141</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6907</v>
+        <v>-0.08459999999999998</v>
       </c>
       <c r="V12" t="n">
         <v>-2.8526</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. LICZNAROWSKI</t>
+          <t>H. MARTORELL TRONCHONI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8104</v>
+        <v>5.1127</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5688</v>
+        <v>3.1499</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2416</v>
+        <v>1.9627</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1563</v>
+        <v>0.5205999999999997</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5048</v>
+        <v>0.871</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6516</v>
+        <v>-0.3506999999999997</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3854</v>
+        <v>2.4063</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1323</v>
+        <v>2.5849</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5177</v>
+        <v>-0.1787</v>
       </c>
       <c r="M13" t="n">
-        <v>1.5417</v>
+        <v>-1.8857</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3725</v>
+        <v>-1.7138</v>
       </c>
       <c r="O13" t="n">
-        <v>1.1692</v>
+        <v>-0.1719999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3774</v>
+        <v>3.9627</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3209</v>
+        <v>6.793200000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3332</v>
+        <v>4.1236</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6525</v>
+        <v>3.3103</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6808</v>
+        <v>0.8132999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9434</v>
+        <v>-3.4941</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2452</v>
+        <v>0.2638000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3018</v>
+        <v>-3.758</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H. MARTORELL TRONCHONI</t>
+          <t>M. LICZNAROWSKI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7461</v>
+        <v>3.6944</v>
       </c>
       <c r="E14" t="n">
-        <v>1.707</v>
+        <v>0.4528</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0391</v>
+        <v>3.2416</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5205999999999997</v>
+        <v>1.1563</v>
       </c>
       <c r="H14" t="n">
-        <v>0.871</v>
+        <v>0.5048</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3506999999999997</v>
+        <v>0.6516</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4063</v>
+        <v>-0.3854</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5849</v>
+        <v>0.1323</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1787</v>
+        <v>-0.5177</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8857</v>
+        <v>1.5417</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.7138</v>
+        <v>0.3725</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1719999999999999</v>
+        <v>1.1692</v>
       </c>
       <c r="P14" t="n">
-        <v>3.9627</v>
+        <v>0.3774</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.8305</v>
+        <v>-0.9435</v>
       </c>
       <c r="R14" t="n">
-        <v>6.793200000000001</v>
+        <v>1.3209</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7572</v>
+        <v>1.2173</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8674</v>
+        <v>0.5365</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1103</v>
+        <v>0.6808</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.4941</v>
+        <v>0.9434</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2638000000000001</v>
+        <v>1.2452</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.758</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9906</v>
+        <v>2.1591</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2094</v>
+        <v>1.4043</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7812</v>
+        <v>0.7548</v>
       </c>
       <c r="G15" t="n">
         <v>2.1629</v>
@@ -1624,13 +1624,13 @@
         <v>0.7548</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0165</v>
+        <v>0.1849</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4267</v>
+        <v>0.6216</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4103</v>
+        <v>-0.4367</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.1204</v>
+        <v>-2.0494</v>
       </c>
       <c r="E16" t="n">
-        <v>0.06</v>
+        <v>0.1575</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.1804</v>
+        <v>-2.2068</v>
       </c>
       <c r="G16" t="n">
         <v>1.2926</v>
@@ -1702,13 +1702,13 @@
         <v>0.1887</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1341</v>
+        <v>0.205</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4732</v>
+        <v>0.5706</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3391</v>
+        <v>-0.3656</v>
       </c>
       <c r="V16" t="n">
         <v>-2.7922</v>
@@ -1735,13 +1735,13 @@
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.292299999999999</v>
+        <v>-2.3468</v>
       </c>
       <c r="E17" t="n">
-        <v>-8.4117</v>
+        <v>-5.8584</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1192</v>
+        <v>3.5115</v>
       </c>
       <c r="G17" t="n">
         <v>-7.4487</v>
@@ -1780,13 +1780,13 @@
         <v>7.925400000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.1083</v>
+        <v>0.8375</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.7455</v>
+        <v>0.8080999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3626</v>
+        <v>0.02970000000000005</v>
       </c>
       <c r="V17" t="n">
         <v>1.2452</v>
@@ -1813,13 +1813,13 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>573.903</v>
+        <v>596.3985</v>
       </c>
       <c r="E18" t="n">
-        <v>362.188</v>
+        <v>371.6918</v>
       </c>
       <c r="F18" t="n">
-        <v>211.7155</v>
+        <v>224.708</v>
       </c>
       <c r="G18" t="n">
         <v>294.3896</v>
@@ -1858,13 +1858,13 @@
         <v>468.9195</v>
       </c>
       <c r="S18" t="n">
-        <v>120.057</v>
+        <v>142.5519</v>
       </c>
       <c r="T18" t="n">
-        <v>95.0112</v>
+        <v>104.5166</v>
       </c>
       <c r="U18" t="n">
-        <v>25.0442</v>
+        <v>38.0364</v>
       </c>
       <c r="V18" t="n">
         <v>46.23710000000001</v>
